--- a/Sensitivity analysis/sensitivity.xlsx
+++ b/Sensitivity analysis/sensitivity.xlsx
@@ -385,16 +385,16 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0.2065986394557823</v>
+        <v>0.07675</v>
       </c>
       <c r="B2">
-        <v>6.101270598773862E-32</v>
+        <v>6.249809659430056E-148</v>
       </c>
       <c r="C2">
-        <v>0.8355328798185941</v>
+        <v>0.267125</v>
       </c>
       <c r="D2">
-        <v>9.586181619044839E-44</v>
+        <v>8.221766729351771E-16</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -402,16 +402,16 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.1617913832199546</v>
+        <v>0.07665</v>
       </c>
       <c r="B3">
-        <v>2.442188945252095E-51</v>
+        <v>5.55361142660021E-148</v>
       </c>
       <c r="C3">
-        <v>0.8350340136054422</v>
+        <v>0.268025</v>
       </c>
       <c r="D3">
-        <v>1.629073293436991E-43</v>
+        <v>1.130642950178411E-15</v>
       </c>
       <c r="E3">
         <v>0.1</v>
@@ -419,16 +419,16 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.1631065759637188</v>
+        <v>0.07615</v>
       </c>
       <c r="B4">
-        <v>9.000932955221528E-52</v>
+        <v>1.059386735532409E-150</v>
       </c>
       <c r="C4">
-        <v>0.834920634920635</v>
+        <v>0.2692</v>
       </c>
       <c r="D4">
-        <v>1.877496271681927E-43</v>
+        <v>1.693213404095136E-15</v>
       </c>
       <c r="E4">
         <v>0.2</v>
@@ -436,16 +436,16 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.1773922902494331</v>
+        <v>0.07502499999999999</v>
       </c>
       <c r="B5">
-        <v>1.319614089068267E-44</v>
+        <v>3.581974376170396E-156</v>
       </c>
       <c r="C5">
-        <v>0.8345804988662131</v>
+        <v>0.27035</v>
       </c>
       <c r="D5">
-        <v>2.862366556813293E-43</v>
+        <v>2.440342853915957E-15</v>
       </c>
       <c r="E5">
         <v>0.3</v>
@@ -453,16 +453,16 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.2002947845804989</v>
+        <v>0.0738</v>
       </c>
       <c r="B6">
-        <v>4.471805742489143E-35</v>
+        <v>7.847502542005518E-162</v>
       </c>
       <c r="C6">
-        <v>0.83437641723356</v>
+        <v>0.271525</v>
       </c>
       <c r="D6">
-        <v>3.607409167273198E-43</v>
+        <v>3.605119921008042E-15</v>
       </c>
       <c r="E6">
         <v>0.4</v>
@@ -470,16 +470,16 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.2337414965986395</v>
+        <v>0.0746</v>
       </c>
       <c r="B7">
-        <v>1.349147177430513E-24</v>
+        <v>5.30827671044688E-160</v>
       </c>
       <c r="C7">
-        <v>0.8342857142857143</v>
+        <v>0.272775</v>
       </c>
       <c r="D7">
-        <v>3.858239197177781E-43</v>
+        <v>5.397904888690135E-15</v>
       </c>
       <c r="E7">
         <v>0.5</v>
@@ -487,16 +487,16 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.2700226757369614</v>
+        <v>0.075625</v>
       </c>
       <c r="B8">
-        <v>5.972862839187062E-17</v>
+        <v>1.049381985754122E-157</v>
       </c>
       <c r="C8">
-        <v>0.8341269841269842</v>
+        <v>0.2739</v>
       </c>
       <c r="D8">
-        <v>4.648367131542115E-43</v>
+        <v>7.727104453058648E-15</v>
       </c>
       <c r="E8">
         <v>0.6000000000000001</v>
@@ -504,16 +504,16 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.3033560090702948</v>
+        <v>0.07665</v>
       </c>
       <c r="B9">
-        <v>6.126118791652829E-12</v>
+        <v>8.441036066665199E-156</v>
       </c>
       <c r="C9">
-        <v>0.8342176870748299</v>
+        <v>0.274925</v>
       </c>
       <c r="D9">
-        <v>4.099631235050882E-43</v>
+        <v>1.078996734443251E-14</v>
       </c>
       <c r="E9">
         <v>0.7000000000000001</v>
@@ -521,16 +521,16 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.3261224489795919</v>
+        <v>0.075725</v>
       </c>
       <c r="B10">
-        <v>2.856706163916817E-09</v>
+        <v>7.456865717537241E-160</v>
       </c>
       <c r="C10">
-        <v>0.8343990929705215</v>
+        <v>0.2766</v>
       </c>
       <c r="D10">
-        <v>3.343599832972647E-43</v>
+        <v>1.860622646563359E-14</v>
       </c>
       <c r="E10">
         <v>0.8</v>
@@ -538,16 +538,16 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.2247392290249433</v>
+        <v>0.049025</v>
       </c>
       <c r="B11">
-        <v>3.471334631309417E-26</v>
+        <v>3.797453602583531E-259</v>
       </c>
       <c r="C11">
-        <v>0.8348526077097506</v>
+        <v>0.279475</v>
       </c>
       <c r="D11">
-        <v>1.989766120684142E-43</v>
+        <v>4.902739924768368E-14</v>
       </c>
       <c r="E11">
         <v>0.9</v>
@@ -555,16 +555,16 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.3666439909297052</v>
+        <v>0.07845000000000001</v>
       </c>
       <c r="B12">
-        <v>9.670292056756943E-06</v>
+        <v>4.70662260370496E-150</v>
       </c>
       <c r="C12">
-        <v>0.8353061224489796</v>
+        <v>0.2815</v>
       </c>
       <c r="D12">
-        <v>1.198823158292824E-43</v>
+        <v>9.393530759265901E-14</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -609,16 +609,16 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0.2065986394557823</v>
+        <v>0.07675</v>
       </c>
       <c r="B2">
-        <v>6.101270598773862E-32</v>
+        <v>6.249809659430056E-148</v>
       </c>
       <c r="C2">
-        <v>0.8355328798185941</v>
+        <v>0.267125</v>
       </c>
       <c r="D2">
-        <v>9.586181619044839E-44</v>
+        <v>8.221766729351771E-16</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -626,16 +626,16 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.2068934240362812</v>
+        <v>0.07675</v>
       </c>
       <c r="B3">
-        <v>6.774780462059031E-32</v>
+        <v>5.327150390198391E-148</v>
       </c>
       <c r="C3">
-        <v>0.8364172335600907</v>
+        <v>0.262025</v>
       </c>
       <c r="D3">
-        <v>4.245699687408126E-44</v>
+        <v>1.076284550894675E-16</v>
       </c>
       <c r="E3">
         <v>0.1</v>
@@ -643,16 +643,16 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.2073696145124717</v>
+        <v>0.076475</v>
       </c>
       <c r="B4">
-        <v>9.91372756164536E-32</v>
+        <v>6.807415287402822E-149</v>
       </c>
       <c r="C4">
-        <v>0.8375283446712019</v>
+        <v>0.2513</v>
       </c>
       <c r="D4">
-        <v>1.112640920529831E-44</v>
+        <v>1.086878700758105E-18</v>
       </c>
       <c r="E4">
         <v>0.2</v>
@@ -660,16 +660,16 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.2086621315192744</v>
+        <v>0.076225</v>
       </c>
       <c r="B5">
-        <v>2.532294858403066E-31</v>
+        <v>1.172319268877532E-149</v>
       </c>
       <c r="C5">
-        <v>0.8393877551020408</v>
+        <v>0.235275</v>
       </c>
       <c r="D5">
-        <v>1.29753802194774E-45</v>
+        <v>4.986206315605764E-22</v>
       </c>
       <c r="E5">
         <v>0.3</v>
@@ -677,16 +677,16 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.2099092970521542</v>
+        <v>0.076275</v>
       </c>
       <c r="B6">
-        <v>6.518394674157638E-31</v>
+        <v>1.837490935566148E-149</v>
       </c>
       <c r="C6">
-        <v>0.8411111111111111</v>
+        <v>0.217075</v>
       </c>
       <c r="D6">
-        <v>1.750521386472724E-46</v>
+        <v>1.333581425764919E-26</v>
       </c>
       <c r="E6">
         <v>0.4</v>
@@ -694,16 +694,16 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.2110430839002267</v>
+        <v>0.07655000000000001</v>
       </c>
       <c r="B7">
-        <v>1.470812386270831E-30</v>
+        <v>1.271289908841375E-148</v>
       </c>
       <c r="C7">
-        <v>0.8423129251700681</v>
+        <v>0.199125</v>
       </c>
       <c r="D7">
-        <v>4.064506418023986E-47</v>
+        <v>3.56491713877177E-32</v>
       </c>
       <c r="E7">
         <v>0.5</v>
@@ -711,16 +711,16 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.2118367346938775</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="B8">
-        <v>2.52829838701071E-30</v>
+        <v>9.860679491164001E-148</v>
       </c>
       <c r="C8">
-        <v>0.8441043083900227</v>
+        <v>0.18005</v>
       </c>
       <c r="D8">
-        <v>4.88902608132684E-48</v>
+        <v>1.113934597845441E-39</v>
       </c>
       <c r="E8">
         <v>0.6000000000000001</v>
@@ -728,16 +728,16 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.2133106575963719</v>
+        <v>0.07704999999999999</v>
       </c>
       <c r="B9">
-        <v>7.094165236309011E-30</v>
+        <v>5.073039892759223E-147</v>
       </c>
       <c r="C9">
-        <v>0.8454421768707483</v>
+        <v>0.163925</v>
       </c>
       <c r="D9">
-        <v>8.241847633788679E-49</v>
+        <v>2.122440768396808E-47</v>
       </c>
       <c r="E9">
         <v>0.7000000000000001</v>
@@ -745,16 +745,16 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.2143310657596372</v>
+        <v>0.0772</v>
       </c>
       <c r="B10">
-        <v>1.445678410756828E-29</v>
+        <v>1.486407314033218E-146</v>
       </c>
       <c r="C10">
-        <v>0.8466893424036281</v>
+        <v>0.14715</v>
       </c>
       <c r="D10">
-        <v>1.553066268049632E-49</v>
+        <v>1.965073836285049E-57</v>
       </c>
       <c r="E10">
         <v>0.8</v>
@@ -762,16 +762,16 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.2151473922902494</v>
+        <v>0.07785</v>
       </c>
       <c r="B11">
-        <v>2.493397610476529E-29</v>
+        <v>6.576771942982111E-145</v>
       </c>
       <c r="C11">
-        <v>0.8480045351473923</v>
+        <v>0.1332</v>
       </c>
       <c r="D11">
-        <v>2.969957927613242E-50</v>
+        <v>9.963510126354023E-68</v>
       </c>
       <c r="E11">
         <v>0.9</v>
@@ -779,16 +779,16 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.2166213151927438</v>
+        <v>0.07875</v>
       </c>
       <c r="B12">
-        <v>7.093546336518103E-29</v>
+        <v>2.511927054311519E-142</v>
       </c>
       <c r="C12">
-        <v>0.849092970521542</v>
+        <v>0.121825</v>
       </c>
       <c r="D12">
-        <v>7.019613725967802E-51</v>
+        <v>4.509843475295553E-78</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -833,16 +833,16 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0.2065986394557823</v>
+        <v>0.07675</v>
       </c>
       <c r="B2">
-        <v>6.101270598773862E-32</v>
+        <v>6.249809659430056E-148</v>
       </c>
       <c r="C2">
-        <v>0.8355328798185941</v>
+        <v>0.267125</v>
       </c>
       <c r="D2">
-        <v>9.586181619044839E-44</v>
+        <v>8.221766729351771E-16</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -850,16 +850,16 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.1619274376417233</v>
+        <v>0.0767</v>
       </c>
       <c r="B3">
-        <v>2.598605823069527E-51</v>
+        <v>5.009849373567243E-148</v>
       </c>
       <c r="C3">
-        <v>0.8360090702947846</v>
+        <v>0.26315</v>
       </c>
       <c r="D3">
-        <v>6.475420406226196E-44</v>
+        <v>1.644334302173976E-16</v>
       </c>
       <c r="E3">
         <v>0.1</v>
@@ -867,16 +867,16 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.1636507936507937</v>
+        <v>0.076275</v>
       </c>
       <c r="B4">
-        <v>1.68873627565152E-51</v>
+        <v>9.664152364348379E-151</v>
       </c>
       <c r="C4">
-        <v>0.8368934240362812</v>
+        <v>0.253775</v>
       </c>
       <c r="D4">
-        <v>2.285913117827161E-44</v>
+        <v>2.990672519063511E-18</v>
       </c>
       <c r="E4">
         <v>0.2</v>
@@ -884,16 +884,16 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.1780498866213152</v>
+        <v>0.07552499999999999</v>
       </c>
       <c r="B5">
-        <v>2.360636066179758E-44</v>
+        <v>6.148226689886058E-155</v>
       </c>
       <c r="C5">
-        <v>0.8384126984126984</v>
+        <v>0.23895</v>
       </c>
       <c r="D5">
-        <v>4.127510613340976E-45</v>
+        <v>2.872836630435873E-21</v>
       </c>
       <c r="E5">
         <v>0.3</v>
@@ -901,16 +901,16 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.2014965986394558</v>
+        <v>0.07527499999999999</v>
       </c>
       <c r="B6">
-        <v>9.257284023466997E-35</v>
+        <v>1.133337944778751E-157</v>
       </c>
       <c r="C6">
-        <v>0.8400226757369614</v>
+        <v>0.221925</v>
       </c>
       <c r="D6">
-        <v>7.013221382236057E-46</v>
+        <v>2.278909901772505E-25</v>
       </c>
       <c r="E6">
         <v>0.4</v>
@@ -918,16 +918,16 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.2358503401360544</v>
+        <v>0.077125</v>
       </c>
       <c r="B7">
-        <v>3.422135113933404E-24</v>
+        <v>6.457212406250649E-153</v>
       </c>
       <c r="C7">
-        <v>0.8415646258503401</v>
+        <v>0.20505</v>
       </c>
       <c r="D7">
-        <v>1.085493760271526E-46</v>
+        <v>2.300940047474778E-30</v>
       </c>
       <c r="E7">
         <v>0.5</v>
@@ -935,16 +935,16 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.2743310657596372</v>
+        <v>0.079275</v>
       </c>
       <c r="B8">
-        <v>2.859295374247295E-16</v>
+        <v>1.01754753986351E-146</v>
       </c>
       <c r="C8">
-        <v>0.8441043083900227</v>
+        <v>0.18755</v>
       </c>
       <c r="D8">
-        <v>4.96868374802425E-48</v>
+        <v>9.560531725473252E-37</v>
       </c>
       <c r="E8">
         <v>0.6000000000000001</v>
@@ -952,16 +952,16 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.3097505668934241</v>
+        <v>0.0815</v>
       </c>
       <c r="B9">
-        <v>3.571663782415907E-11</v>
+        <v>1.001066245216265E-141</v>
       </c>
       <c r="C9">
-        <v>0.8456235827664399</v>
+        <v>0.171925</v>
       </c>
       <c r="D9">
-        <v>7.536343949427495E-49</v>
+        <v>1.821035536400782E-43</v>
       </c>
       <c r="E9">
         <v>0.7000000000000001</v>
@@ -969,16 +969,16 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.3349886621315193</v>
+        <v>0.08155</v>
       </c>
       <c r="B10">
-        <v>2.164930198337636E-08</v>
+        <v>1.674356428621017E-142</v>
       </c>
       <c r="C10">
-        <v>0.846530612244898</v>
+        <v>0.156225</v>
       </c>
       <c r="D10">
-        <v>2.018076463697221E-49</v>
+        <v>9.548463948282723E-52</v>
       </c>
       <c r="E10">
         <v>0.8</v>
@@ -986,16 +986,16 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.2343764172335601</v>
+        <v>0.05205</v>
       </c>
       <c r="B11">
-        <v>9.148969845943511E-24</v>
+        <v>7.687619247725295E-238</v>
       </c>
       <c r="C11">
-        <v>0.8479591836734693</v>
+        <v>0.144025</v>
       </c>
       <c r="D11">
-        <v>3.870931983766961E-50</v>
+        <v>2.621684680439435E-59</v>
       </c>
       <c r="E11">
         <v>0.9</v>
@@ -1003,16 +1003,16 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.3809297052154195</v>
+        <v>0.08497499999999999</v>
       </c>
       <c r="B12">
-        <v>9.08057834175827E-05</v>
+        <v>5.454072032894635E-133</v>
       </c>
       <c r="C12">
-        <v>0.8497959183673469</v>
+        <v>0.13415</v>
       </c>
       <c r="D12">
-        <v>3.847074434359564E-51</v>
+        <v>1.284649567049324E-66</v>
       </c>
       <c r="E12">
         <v>1</v>
